--- a/Entrega_02/Betanzo_Integrante_01_database_02/adquisiciones_tencent.xlsx
+++ b/Entrega_02/Betanzo_Integrante_01_database_02/adquisiciones_tencent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abeta\Documents\GitHub\Chinese-Propaganda\Entrega_02\Betanzo_Integrante_01_database_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45987FC1-777F-4AFF-AE81-300F5EFC05D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E34A28-7D32-4AB3-AA07-1905094798B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9285" yWindow="0" windowWidth="19620" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="210" windowWidth="27195" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="57">
   <si>
     <t>Empresa adquirida</t>
   </si>
@@ -91,6 +91,111 @@
   </si>
   <si>
     <t>3.8</t>
+  </si>
+  <si>
+    <t>Leyou Technologies</t>
+  </si>
+  <si>
+    <t>Certain Affinity</t>
+  </si>
+  <si>
+    <t>Hong Kong, China</t>
+  </si>
+  <si>
+    <t>Supercell</t>
+  </si>
+  <si>
+    <t>84.3</t>
+  </si>
+  <si>
+    <t>Monto de transacción (en millones de USD)</t>
+  </si>
+  <si>
+    <t>Desconocido</t>
+  </si>
+  <si>
+    <t>Techland</t>
+  </si>
+  <si>
+    <t>Polonia</t>
+  </si>
+  <si>
+    <t>Turtle Rock Studios</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>57.1</t>
+  </si>
+  <si>
+    <t>Vantage Studios (Subsidiaria de Ubisoft)</t>
+  </si>
+  <si>
+    <t>26.32</t>
+  </si>
+  <si>
+    <t>Inflexion Games</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>Platinum Games</t>
+  </si>
+  <si>
+    <t>Yager</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>Frontier Developments</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>23.57</t>
+  </si>
+  <si>
+    <t>Kakao</t>
+  </si>
+  <si>
+    <t>Paradox Interactive</t>
+  </si>
+  <si>
+    <t>Fatshark</t>
+  </si>
+  <si>
+    <t>Funcom</t>
+  </si>
+  <si>
+    <t>Sharkmob</t>
+  </si>
+  <si>
+    <t>Discord</t>
+  </si>
+  <si>
+    <t>13.5</t>
+  </si>
+  <si>
+    <t>Kakao Games</t>
+  </si>
+  <si>
+    <t>46.4</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>Comprador</t>
+  </si>
+  <si>
+    <t>Tencent</t>
   </si>
 </sst>
 </file>
@@ -126,8 +231,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,150 +519,554 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="2" max="3" width="37.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="D2" s="1">
         <v>2011</v>
       </c>
-      <c r="D2">
+      <c r="E2" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="1">
         <v>2012</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F3" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="D4" s="1">
         <v>2017</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="1">
         <v>2022</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F5" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E6" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="1">
         <v>2018</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F7" s="2">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="C8">
+      <c r="D9" s="1">
         <v>2012</v>
       </c>
-      <c r="D8">
+      <c r="E9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="C9">
+      <c r="D10" s="1">
         <v>2018</v>
       </c>
-      <c r="D9">
+      <c r="E10" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="C10">
+      <c r="D11" s="1">
         <v>2021</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E11" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E12" s="1">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E13" s="1">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E15" s="1">
+        <v>67</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E16" s="1">
+        <v>100</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E17" s="1">
+        <v>100</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E20" s="1">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2016</v>
+      </c>
+      <c r="E23" s="1">
+        <v>10</v>
+      </c>
+      <c r="F23" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E25" s="1">
+        <v>100</v>
+      </c>
+      <c r="F25" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E26" s="1">
+        <v>100</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="1">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
